--- a/EXCEL/Data/Figur_1+2/Figur1_api_output.xlsx
+++ b/EXCEL/Data/Figur_1+2/Figur1_api_output.xlsx
@@ -85,7 +85,7 @@
     <t>Datasæt 01 2018</t>
   </si>
   <si>
-    <t>Kørsel 8.4.2026 13.55.19</t>
+    <t>Kørsel 14.4.2026 12.26.47</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
@@ -634,13 +634,13 @@
         <v>13</v>
       </c>
       <c r="B4" s="6">
-        <v>119193.13281617513</v>
+        <v>119193.13281617514</v>
       </c>
       <c r="C4" s="6">
-        <v>120500.02015653135</v>
+        <v>120500.02015653136</v>
       </c>
       <c r="D4" s="6">
-        <v>122103.37572755637</v>
+        <v>122103.37572755635</v>
       </c>
       <c r="E4" s="6">
         <v>128186.59794914271</v>
@@ -649,16 +649,16 @@
         <v>131915.48695585536</v>
       </c>
       <c r="G4" s="6">
-        <v>128846.83640513338</v>
+        <v>128846.83640513336</v>
       </c>
       <c r="H4" s="6">
         <v>129783.08717542916</v>
       </c>
       <c r="I4" s="6">
-        <v>131130.63889557088</v>
+        <v>131130.6388955709</v>
       </c>
       <c r="J4" s="6">
-        <v>133537.63019017054</v>
+        <v>133537.63019017057</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -669,28 +669,28 @@
         <v>12405.144168625866</v>
       </c>
       <c r="C5" s="8">
-        <v>12433.889366499796</v>
+        <v>12433.889366499798</v>
       </c>
       <c r="D5" s="8">
         <v>12557.495233184132</v>
       </c>
       <c r="E5" s="8">
-        <v>13225.388547299774</v>
+        <v>13225.388547299775</v>
       </c>
       <c r="F5" s="8">
-        <v>13423.704288819554</v>
+        <v>13423.704288819552</v>
       </c>
       <c r="G5" s="8">
         <v>13367.315188585368</v>
       </c>
       <c r="H5" s="8">
-        <v>13376.643199108383</v>
+        <v>13376.643199108385</v>
       </c>
       <c r="I5" s="8">
         <v>13419.086801470405</v>
       </c>
       <c r="J5" s="8">
-        <v>13821.984093703517</v>
+        <v>13821.984093703515</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -698,13 +698,13 @@
         <v>15</v>
       </c>
       <c r="B6" s="6">
-        <v>27254.629531232033</v>
+        <v>27254.62953123203</v>
       </c>
       <c r="C6" s="6">
-        <v>27242.83821180233</v>
+        <v>27242.838211802326</v>
       </c>
       <c r="D6" s="6">
-        <v>27517.651209443895</v>
+        <v>27517.6512094439</v>
       </c>
       <c r="E6" s="6">
         <v>29134.004179375428</v>
@@ -713,7 +713,7 @@
         <v>30484.169790812262</v>
       </c>
       <c r="G6" s="6">
-        <v>29587.82435639149</v>
+        <v>29587.824356391495</v>
       </c>
       <c r="H6" s="6">
         <v>29852.955726384465</v>
@@ -722,7 +722,7 @@
         <v>30006.037991796115</v>
       </c>
       <c r="J6" s="6">
-        <v>30619.89307702809</v>
+        <v>30619.893077028086</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -730,7 +730,7 @@
         <v>16</v>
       </c>
       <c r="B7" s="8">
-        <v>24841.622235258787</v>
+        <v>24841.62223525879</v>
       </c>
       <c r="C7" s="8">
         <v>25285.149299462428</v>
@@ -739,22 +739,22 @@
         <v>25726.867990382365</v>
       </c>
       <c r="E7" s="8">
-        <v>26877.50490208508</v>
+        <v>26877.504902085075</v>
       </c>
       <c r="F7" s="8">
-        <v>27380.872419473384</v>
+        <v>27380.872419473388</v>
       </c>
       <c r="G7" s="8">
-        <v>26560.169205454873</v>
+        <v>26560.169205454877</v>
       </c>
       <c r="H7" s="8">
         <v>26648.593029038468</v>
       </c>
       <c r="I7" s="8">
-        <v>26981.897799671282</v>
+        <v>26981.89779967128</v>
       </c>
       <c r="J7" s="8">
-        <v>27437.650311132078</v>
+        <v>27437.65031113208</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -771,10 +771,10 @@
         <v>39412.585160920986</v>
       </c>
       <c r="E8" s="6">
-        <v>41437.232412469675</v>
+        <v>41437.23241246967</v>
       </c>
       <c r="F8" s="6">
-        <v>42139.14860991171</v>
+        <v>42139.1486099117</v>
       </c>
       <c r="G8" s="6">
         <v>41117.917231175226</v>
@@ -786,7 +786,7 @@
         <v>41965.29947411081</v>
       </c>
       <c r="J8" s="6">
-        <v>42500.5795530325</v>
+        <v>42500.579553032505</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -797,7 +797,7 @@
         <v>15789.608609562769</v>
       </c>
       <c r="C9" s="8">
-        <v>15684.546297553707</v>
+        <v>15684.546297553705</v>
       </c>
       <c r="D9" s="8">
         <v>15998.882328613257</v>
@@ -806,7 +806,7 @@
         <v>16656.82466108685</v>
       </c>
       <c r="F9" s="8">
-        <v>17605.566450750164</v>
+        <v>17605.566450750168</v>
       </c>
       <c r="G9" s="8">
         <v>17323.430604038127</v>
@@ -815,10 +815,10 @@
         <v>17594.567608464902</v>
       </c>
       <c r="I9" s="8">
-        <v>17876.659547920317</v>
+        <v>17876.659547920313</v>
       </c>
       <c r="J9" s="8">
-        <v>18277.972419260692</v>
+        <v>18277.972419260695</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
